--- a/static/data/database/SS1_Students.xlsx
+++ b/static/data/database/SS1_Students.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SS1 Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SS1 Students'!$A$1:$H$114</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SS1 Students'!$A$1:$H$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -473,27 +473,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>std234</t>
+          <t>std160</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADEYEMI</t>
+          <t>AZEEM</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>FUAD</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>FAUZAN</t>
-        </is>
-      </c>
+          <t>ADETUNJI</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>07060774164</t>
+          <t>08136162408</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -515,27 +511,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>std235</t>
+          <t>std161</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>ABDUL</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ADAM</t>
+          <t>UMAR</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ZAID</t>
+          <t>ALECHENZI</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>08132389615</t>
+          <t>07069593719</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -557,27 +553,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>std236</t>
+          <t>std162</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ISAH</t>
+          <t>ABDULHAFIZ</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ABBAS</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AHMAD</t>
-        </is>
-      </c>
+          <t>AMINU</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>09130680040</t>
+          <t>08035976838</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -599,32 +591,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>std237</t>
+          <t>std163</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KAKILI</t>
+          <t>AISHA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ALIYU</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ASHRAF</t>
+          <t>ABDULLAHI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>08035115628</t>
+          <t>08031579478</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -641,27 +633,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>std238</t>
+          <t>std164</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>ALHASSAN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>MUHAMMAD</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>TIJJANI</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>SULAIMAN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>08036065686</t>
+          <t>08033310111</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -683,32 +675,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>std239</t>
+          <t>std165</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>YAHAYA</t>
+          <t>AMIRA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MAARA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>UMAR</t>
-        </is>
-      </c>
+          <t>RAJI</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>07067509810</t>
+          <t>08067444552</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -725,27 +713,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>std240</t>
+          <t>std166</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ABDULQADIR</t>
+          <t>ABUSALMA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TEMITOPE</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>UTHMAN</t>
-        </is>
-      </c>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>08023826740</t>
+          <t>07066774164</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -767,12 +751,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>std241</t>
+          <t>std167</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>ABDULAZEEZ</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -780,14 +764,10 @@
           <t>IBRAHIM</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>MUSA</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08032140551</t>
+          <t>08057727924</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -809,32 +789,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>std242</t>
+          <t>std168</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SHEHU</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AHMAD</t>
+          <t>ZARAH</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>JIBRIL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08066027728</t>
+          <t>08036668605</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -851,32 +831,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>std243</t>
+          <t>std169</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TUKUR</t>
+          <t>FIRDAUSI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>AL-AMIN</t>
-        </is>
-      </c>
+          <t>KASHEM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>08184501992</t>
+          <t>07033452007</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -893,27 +869,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>std244</t>
+          <t>std170</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>HANIFAH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SALIHU</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>MARYAM M.</t>
-        </is>
-      </c>
+          <t>ADETOYE</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>08037567178</t>
+          <t>07068505744</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -935,32 +907,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>std245</t>
+          <t>std171</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ALIYU</t>
+          <t>IMRAN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ASHEZI</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>YASMIN</t>
-        </is>
-      </c>
+          <t>DAHIRU</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>08066686000</t>
+          <t>07066666860</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -977,32 +945,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>std246</t>
+          <t>std172</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KOLE</t>
+          <t>ISMA'IL</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MUHAMMED</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>HAFSAT</t>
-        </is>
-      </c>
+          <t>ABDULKABIR</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>08140739244</t>
+          <t>07064645550</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1019,27 +983,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>std247</t>
+          <t>std173</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>AMINU</t>
+          <t>KAMILAH</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MSHEELIA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>KHADIJAH</t>
-        </is>
-      </c>
+          <t>RAJI</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>08033155739</t>
+          <t>080334971256</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1061,23 +1021,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>std248</t>
+          <t>std174</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GBADAMOSI</t>
+          <t>KHADIJA</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RASHEEDAH</t>
+          <t>YERIMA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>08035872403</t>
+          <t>08162354054</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1099,32 +1059,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>std249</t>
+          <t>std175</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DIKKO</t>
+          <t>MAHMUD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ISMAIL</t>
+          <t>KABIRU</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>MUKTAR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>08081955353</t>
+          <t>08035112956</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1141,27 +1101,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>std250</t>
+          <t>std176</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>KABIDO</t>
+          <t>MUHSINA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MUSA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>RAHAMA</t>
-        </is>
-      </c>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>08138424118</t>
+          <t>07038251084</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1183,32 +1139,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>std251</t>
+          <t>std177</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ADEROGBA</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ADELESO</t>
+          <t>SAMIR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>HASSANA</t>
+          <t>ZAIYANU</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>08038204448</t>
+          <t>07030927742</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1225,27 +1181,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>std252</t>
+          <t>std178</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ADEMOYE</t>
+          <t>NA'IMA</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ABIOLA</t>
+          <t>AUWAL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FATHIA</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08038184758</t>
+          <t>08033371313</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1267,27 +1223,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>std253</t>
+          <t>std179</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>YAHAYA</t>
+          <t>NANA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>AUWAL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AISHA</t>
+          <t>ABDULHAKEEM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>07063498835</t>
+          <t>08036544182</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1309,32 +1265,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>std254</t>
+          <t>std180</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>RAJI</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>TUKUR</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MUFIDAT</t>
+          <t>KAWU</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>07064220549</t>
+          <t>07061800414</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1351,27 +1307,23 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>std255</t>
+          <t>std181</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ISMAIL</t>
+          <t>RUTH</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ISAH</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>FAIZA</t>
-        </is>
-      </c>
+          <t>EZE</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>07063619332</t>
+          <t>08063155872</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1393,27 +1345,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>std256</t>
+          <t>std182</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>RUKKAIYA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EFUA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>AMIRA</t>
-        </is>
-      </c>
+          <t>ABAMAMMAN</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>08033410008</t>
+          <t>08036134213</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1435,27 +1383,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>std257</t>
+          <t>std183</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OMADEFU</t>
+          <t>YUSRA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ASIBI</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>AMIRA</t>
-        </is>
-      </c>
+          <t>ABDULRASHEED</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>08036057258</t>
+          <t>08023797649</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1477,23 +1421,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>std258</t>
+          <t>std184</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ADEYEMI</t>
+          <t>ZAINAB</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEBBAHTULLAH</t>
+          <t>ALIYU</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>08036261741</t>
+          <t>09186644664</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1515,27 +1459,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>std259</t>
+          <t>std185</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DAMUSA</t>
+          <t>ZAKIYYAH</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UFEDOTOH</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NANA K.</t>
+          <t>OMONYE</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>08065376751</t>
+          <t>08035290331</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1557,27 +1501,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>std260</t>
+          <t>std186</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GALADIMA</t>
+          <t>KHADIJA</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USMAN</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>KHADIJA</t>
-        </is>
-      </c>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>08144826092</t>
+          <t>09164925212</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1599,28 +1539,32 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>std261</t>
+          <t>std187</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UMMULKHAIR</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>YUSUF</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>UMAR</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>08030569524</t>
+          <t>07031940146</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1637,27 +1581,23 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>std262</t>
+          <t>std188</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TAJUDEEN</t>
+          <t>ADAMU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ASIWAJU</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>ABDULBASIT</t>
-        </is>
-      </c>
+          <t>YAKUBU</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>080095613348</t>
+          <t>09022340559</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1679,32 +1619,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>std263</t>
+          <t>std189</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MUHAMMED</t>
+          <t>MOHAMMAD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>OYIZA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>KHAIRET</t>
-        </is>
-      </c>
+          <t>NASIR</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>08072424291</t>
+          <t>07064493655</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1721,23 +1657,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>std264</t>
+          <t>std190</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>HABIBULLAH</t>
+          <t>AHMAD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ABDULMALIK</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AFFAN</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>08065544064</t>
+          <t>08068694226</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1759,23 +1699,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>std265</t>
+          <t>std191</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BABAKURA</t>
+          <t>ABDUL-QADIR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TIJJANI</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
+          <t>KHALIFA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>KABIR</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>08067045013</t>
+          <t>08034800600</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1785,7 +1729,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1797,23 +1741,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>std266</t>
+          <t>std192</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MUSA</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>TAHIR</t>
+          <t>ABDULWAHAB</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>08066441344</t>
+          <t>08077229624</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1823,7 +1767,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1835,23 +1779,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>std267</t>
+          <t>std193</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>KABIR</t>
+          <t>USMAN</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SAIDUBABA</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>ADAMU</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ISHAQ</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>09119851571</t>
+          <t>08131449884</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1861,7 +1809,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1873,27 +1821,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>std268</t>
+          <t>std194</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SHEHU</t>
+          <t>IRFAN</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RAMALAN</t>
+          <t>FARUK</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SAABIR</t>
+          <t>IDIARO</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>08035927011</t>
+          <t>08033707456</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1903,7 +1851,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1915,27 +1863,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>std269</t>
+          <t>std195</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AL-AMIN</t>
+          <t>OMALE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>O.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>AHMED</t>
-        </is>
-      </c>
+          <t>JORDAN</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>08136552705</t>
+          <t>08073173763</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1945,7 +1889,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1957,33 +1901,37 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>std270</t>
+          <t>std196</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ZAHARADEEN</t>
+          <t>UMMULKULTHUM</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UMAR</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>HAYATU</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>WAZIRI</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08035944688</t>
+          <t>08026329671</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1995,37 +1943,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>std271</t>
+          <t>std197</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AMINU</t>
+          <t>MUHAMMED</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>MUSA</t>
-        </is>
-      </c>
+          <t>HAUWA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>08032889558</t>
+          <t>08033697673</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2037,37 +1981,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>std272</t>
+          <t>std198</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SADIQ</t>
+          <t>SUMIA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ISMAIL</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
+          <t>MOMOD</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>08033587358</t>
+          <t>07064174881</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2079,23 +2019,27 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>std273</t>
+          <t>std199</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>IDRIS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JAMILA</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>MARYAM</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>RABIU</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>08036272740</t>
+          <t>08036077039</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2105,7 +2049,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2117,27 +2061,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>std274</t>
+          <t>std200</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ABDURRAHMAN</t>
+          <t>ABBAKURA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NUMAT</t>
+          <t>FATIMAH</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>MAIMUNAT</t>
+          <t>ALI</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>08036040662</t>
+          <t>08032167508</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2147,7 +2091,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2159,27 +2103,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>std275</t>
+          <t>std201</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SAMBO</t>
+          <t>ISMAIL</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HAJARA</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>AMINU</t>
-        </is>
-      </c>
+          <t>LAMIA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>08035887544</t>
+          <t>07063619332</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2189,7 +2129,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2201,27 +2141,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>std276</t>
+          <t>std202</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SANI</t>
+          <t>IDOWU</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HAFSA</t>
+          <t>NIMATULLAHI</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>A.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>07036576765</t>
+          <t>08036888250</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2231,7 +2171,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2243,37 +2183,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>std277</t>
+          <t>std203</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SALISU</t>
+          <t>SUNUSI</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NANA</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>ASMAU</t>
-        </is>
-      </c>
+          <t>AMIR</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>07089903318</t>
+          <t>08166677184</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2285,27 +2221,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>std278</t>
+          <t>std204</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>ISMAIL</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ZAINAB</t>
+          <t>UMMU</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>AMINU</t>
+          <t>SHURAIHA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>08055262097</t>
+          <t>08032892838</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2315,7 +2251,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2327,33 +2263,37 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>std279</t>
+          <t>std205</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AMATULLAH</t>
+          <t>UTHMAN</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ABDULMALIK</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>JAWAD</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>08036495912</t>
+          <t>08065474565</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2365,27 +2305,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>std280</t>
+          <t>std206</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IKAKA</t>
+          <t>MUKHTAR</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AHMED</t>
+          <t>AISHA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BILKISU</t>
+          <t>AHMAD</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>08033884440</t>
+          <t>08139191130</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2395,7 +2335,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2407,27 +2347,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>std281</t>
+          <t>std207</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>OLOPADE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KABIR</t>
+          <t>ABDUL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>MUKHTAR</t>
+          <t>WARIS</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>08033912352</t>
+          <t>08165453077</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2437,7 +2377,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2449,7 +2389,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>std282</t>
+          <t>std208</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2459,13 +2399,17 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HUSSAIN</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr"/>
+          <t>IDRIS</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ABDULLAHI</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>07035663576</t>
+          <t>08093871791</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2475,7 +2419,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2487,33 +2431,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>std283</t>
+          <t>std209</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BASHIR</t>
+          <t>ABBAKURA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MAHMUD</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
+          <t>FATIMA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>ZAHRA</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>08032181310</t>
+          <t>08032109299</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2525,37 +2473,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>std284</t>
+          <t>std210</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AMINU</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YASSAR</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
+          <t>ABDULJABBAR</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>08157275454</t>
+          <t>08027950448</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SS1_SILVER</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2567,33 +2511,37 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>std285</t>
+          <t>std211</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>AISHA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SA'AD</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>ABUBAKAR</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>GIREI</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>08034000882</t>
+          <t>08036232351</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2605,37 +2553,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>std286</t>
+          <t>std212</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ABAHI</t>
+          <t>YUSRAH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WONDA</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>U. ABDULSAMAD</t>
+          <t>A.</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>08066188131</t>
+          <t>08062602000</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2647,37 +2595,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>std287</t>
+          <t>std213</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SHETTIMA</t>
+          <t>RAMLA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>B.</t>
+          <t>YAHAYA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>MUSTAPHA</t>
+          <t>YAKUBU</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>08026994119</t>
+          <t>08064607626</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2689,37 +2637,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>std288</t>
+          <t>std214</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ADEYEMI</t>
+          <t>SAFEEYAH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MATTHEW</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ADESIRE</t>
+          <t>H.</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>08032190197</t>
+          <t>08028398915</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2731,23 +2679,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>std289</t>
+          <t>std215</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KHAIRAT</t>
+          <t>UMMULKHAIR</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>BADAMASI</t>
+          <t>ZUBAIRU</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>08032245423</t>
+          <t>08035952585</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2757,7 +2705,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2769,33 +2717,37 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>std290</t>
+          <t>std216</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>FAIZA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SULEIMAN</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>MUDARRIFU</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>F.</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>07029636558</t>
+          <t>08015404681</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2807,27 +2759,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>std291</t>
+          <t>std217</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>AISHA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UMAIMAH</t>
+          <t>POPOOLA</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ZHEOMA</t>
+          <t>IREBAMI</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>08035885141</t>
+          <t>07022766863</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2837,7 +2789,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2849,37 +2801,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>std292</t>
+          <t>std218</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SAED</t>
+          <t>HAFSAT</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>A.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>HASSAN</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>08035973912</t>
+          <t>08003805010</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2891,33 +2843,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>std293</t>
+          <t>std219</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AKINLOYE</t>
+          <t>RAYYANNA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GODSWILL</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>ALLI</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ADEJOUN</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>08069353822</t>
+          <t>07067020234</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2929,23 +2885,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>std294</t>
+          <t>std220</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RUKAYYA</t>
+          <t>SAFEEYAH</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr"/>
+          <t>SAEED</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>YAHAYA</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>08027163415</t>
+          <t>08033110134</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2955,7 +2915,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2967,37 +2927,33 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>std295</t>
+          <t>std221</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FARZEENAH</t>
+          <t>ABDULGANIYU</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>T.</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
+          <t>AUDU</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>08033577423</t>
+          <t>08023323811</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3009,33 +2965,33 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>std296</t>
+          <t>std222</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OLAGUNJU</t>
+          <t>ZAYYAN</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FIRDAUS</t>
+          <t>ZAYYAN</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>08138369857</t>
+          <t>07068800574</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3047,33 +3003,37 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>std297</t>
+          <t>std223</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OLUFEMOH</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MUNIRAT</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>AUWAL</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>08026160230</t>
+          <t>08034948449</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3085,37 +3045,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>std298</t>
+          <t>std224</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KHADIJAH</t>
+          <t>MURTALA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>BABAYARO</t>
+          <t>HALIRU</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>MUKHTAR</t>
+          <t>AMBURSA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>07063104355</t>
+          <t>08068067508</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3127,37 +3087,33 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>std299</t>
+          <t>std225</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SABIRAH</t>
+          <t>YAHAYA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HASSAN</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>ABDULLAH</t>
-        </is>
-      </c>
+          <t>HABUFARI</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>08034204648</t>
+          <t>08099944553</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3169,27 +3125,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>std300</t>
+          <t>std226</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>BAWA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AMINU</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>SANJUMA</t>
-        </is>
-      </c>
+          <t>MAHMUD</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>08034132060</t>
+          <t>07068816607</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3199,7 +3151,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3211,23 +3163,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>std301</t>
+          <t>std227</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>FARHAN</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TAHIR</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>07035485005</t>
+          <t>08036422227</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3237,7 +3193,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3249,27 +3205,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>std302</t>
+          <t>std228</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>KOREDE</t>
+          <t>ABBAS</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SALAU</t>
+          <t>ABBAS</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>08166294250</t>
+          <t>07034448544</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3279,7 +3235,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3291,23 +3247,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>std303</t>
+          <t>std229</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ZANSHIRU</t>
+          <t>SANI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>08072602070</t>
+          <t>08030733215</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3317,7 +3273,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3329,37 +3285,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>std304</t>
+          <t>std230</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JUNAIRIYYA</t>
+          <t>SALISU</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>RABIU</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>IDRIS</t>
+          <t>BAYERO</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>07039229772</t>
+          <t>08199944444</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3371,37 +3327,33 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>std305</t>
+          <t>std231</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
+          <t>SALIHU</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
           <t>ABUBAKAR</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>FATIMA</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>JASMINE</t>
-        </is>
-      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>08033365925</t>
+          <t>08035839220</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3413,27 +3365,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>std306</t>
+          <t>std232</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ABDULMALIK</t>
+          <t>ABDULHAMID</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SAMIR</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>AHMAD</t>
-        </is>
-      </c>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>08057265792</t>
+          <t>08072229644</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3443,7 +3391,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3455,37 +3403,33 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>std307</t>
+          <t>std233</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AUWAL</t>
+          <t>ABDULLAHI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AISHA</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
+          <t>DANMALAM</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>08036173202</t>
+          <t>09090424235</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>SS1_GOLD</t>
+          <t>SS1_DIAMOND</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3494,1582 +3438,8 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>std308</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>BENITA</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>PETER</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>08069102556</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>SS1_GOLD</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>std309</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>ISHAQ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>A.</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>QASIM USMAN</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>08033191149</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>SS1_GOLD</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>std310</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>MUHAMMED</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>SHEHU</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>080062447500</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>SS1_GOLD</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>std311</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>LUQMAN</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>ALAMIN</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>07032620527</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>SS1_GOLD</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>std312</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>ABUBAKAR</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>HABIBA</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>08041326079</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>SS1_GOLD</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>std313</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>MUSTAPHA</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>FATIMA</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>08067757775</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>SS1_GOLD</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>std314</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>SANI</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>FAZEELAT</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>08030799725</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>std315</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>SHOFOLUWE</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>O.</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>NEEMATULLAH</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>07066229010</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>std316</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>ABBA</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>MAMMAN</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>FATIMA</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>08039725582</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>std317</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>FUAD</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>ADEYEMI</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>FAUZI</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>080130680040</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>std318</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>BASHIR</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>ABDULLAHI</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>080372667696</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>std319</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>MARAFIA</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>ATTAHIR</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>0817808006</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>std320</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>ADEBAYO</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>DAMILOLA</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>FATHIA</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>090388330432</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>std321</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>SHAMSU</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>ZIYAHULLHAQ</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>08037031114</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>std322</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>JOHN</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>DAVID</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>08034414206</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>std323</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>KOREDE</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>SAMUEL</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>07053262036</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>std324</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>AJAO</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>UMAR</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>07034372559</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>std325</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>ABDULLAHI</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>BELLO</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>ALIYU</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>080369891390</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>std326</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>FARUK</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>NDAYAKO</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>SHAFI</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>08032013860</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>std327</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>SANI</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>WAKILI</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>UMAR</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>080331541112</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>std328</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>ADEYEMI</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>ADENIKE</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>NAJA'A</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>08067371845</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>std329</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>AJAO</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>FAUZIYA</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>08034372559</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>std330</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>ABDULLAHI</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>BELLO</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>SADIQ</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>08036989390</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>std331</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>HASHIM</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>MUHAMMED</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>YUNUS</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>08094198290</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>std332</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>UMAR</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>08037876862</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>std333</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>ISA</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>HAUWA</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>080359150327</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>std334</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>SANUSI</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>SUMAYYA</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>08059706494</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>std335</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>BELLO</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>MARYAM</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>MADINAH</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>08188720987</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>std336</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>AMINU</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>YASSAR</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>USMAN</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>091338237</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>std337</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>MUSBAHU</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>YAKUBU</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>AHMAD</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>080552442908</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>std338</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>ZAYYAN</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>MUHSIN</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>07068866548</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>std339</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>ADESHINA</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>CASSANDRA</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>HABIBA</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>0817251384</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>std340</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>BASHIR</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>MAHMUD</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>HAUWA</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>08036587954</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>std341</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>ALIYU</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AHMAD</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>08085566519</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>std342</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>ALIYU</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>LOLO</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>FATIHA</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>08035899950</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>std343</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>ALIYU</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>SHAFI</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>UMAR</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>0707306375</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>std344</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>ALHASSAN</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>AALIYAH</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>UMMT</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>080550885141</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>std345</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>ABUBAKAR</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AMAL</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>AISHA</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>0803159021</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>std346</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>SANUSI</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>ABDULRAHMAN</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>08020850490</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>SS1_B/C</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>SS1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H114"/>
+  <autoFilter ref="A1:H75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/static/data/database/SS1_Students.xlsx
+++ b/static/data/database/SS1_Students.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SS1 Students" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SS1 Students'!$A$1:$H$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SS1 Students'!$A$1:$H$114</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -473,23 +473,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>std160</t>
+          <t>std234</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AZEEM</t>
+          <t>ADEYEMI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ADETUNJI</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>FUAD</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FAUZAN</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>08136162408</t>
+          <t>07060774164</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,27 +515,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>std161</t>
+          <t>std235</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ABDUL</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UMAR</t>
+          <t>ADAM</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ALECHENZI</t>
+          <t>ZAID</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>07069593719</t>
+          <t>08132389615</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -553,23 +557,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>std162</t>
+          <t>std236</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ABDULHAFIZ</t>
+          <t>ISAH</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AMINU</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>ABBAS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AHMAD</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>08035976838</t>
+          <t>09130680040</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -591,32 +599,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>std163</t>
+          <t>std237</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AISHA</t>
+          <t>KAKILI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>ALIYU</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ABDULLAHI</t>
+          <t>ASHRAF</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>08031579478</t>
+          <t>08035115628</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -633,27 +641,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>std164</t>
+          <t>std238</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ALHASSAN</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>TIJJANI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SULAIMAN</t>
+          <t>UMAR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>08033310111</t>
+          <t>08036065686</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -675,28 +683,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>std165</t>
+          <t>std239</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMIRA</t>
+          <t>YAHAYA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RAJI</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>MAARA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>UMAR</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>08067444552</t>
+          <t>07067509810</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -713,23 +725,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>std166</t>
+          <t>std240</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ABUSALMA</t>
+          <t>ABDULQADIR</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>TEMITOPE</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UTHMAN</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>07066774164</t>
+          <t>08023826740</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -751,12 +767,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>std167</t>
+          <t>std241</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ABDULAZEEZ</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -764,10 +780,14 @@
           <t>IBRAHIM</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MUSA</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>08057727924</t>
+          <t>08032140551</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -789,32 +809,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>std168</t>
+          <t>std242</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>SHEHU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ZARAH</t>
+          <t>AHMAD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>JIBRIL</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>08036668605</t>
+          <t>08066027728</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -831,28 +851,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>std169</t>
+          <t>std243</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>FIRDAUSI</t>
+          <t>TUKUR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KASHEM</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AL-AMIN</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>07033452007</t>
+          <t>08184501992</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -869,23 +893,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>std170</t>
+          <t>std244</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>HANIFAH</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ADETOYE</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>SALIHU</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MARYAM M.</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>07068505744</t>
+          <t>08037567178</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -907,28 +935,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>std171</t>
+          <t>std245</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IMRAN</t>
+          <t>ALIYU</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>DAHIRU</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>ASHEZI</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>YASMIN</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>07066666860</t>
+          <t>08066686000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -945,28 +977,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>std172</t>
+          <t>std246</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ISMA'IL</t>
+          <t>KOLE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ABDULKABIR</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>MUHAMMED</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>HAFSAT</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>07064645550</t>
+          <t>08140739244</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -983,23 +1019,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>std173</t>
+          <t>std247</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KAMILAH</t>
+          <t>AMINU</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RAJI</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>MSHEELIA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>KHADIJAH</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>080334971256</t>
+          <t>08033155739</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1021,23 +1061,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>std174</t>
+          <t>std248</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KHADIJA</t>
+          <t>GBADAMOSI</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>YERIMA</t>
+          <t>RASHEEDAH</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>08162354054</t>
+          <t>08035872403</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1059,32 +1099,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>std175</t>
+          <t>std249</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MAHMUD</t>
+          <t>DIKKO</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>KABIRU</t>
+          <t>ISMAIL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MUKTAR</t>
+          <t>FATIMA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>08035112956</t>
+          <t>08081955353</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1101,23 +1141,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>std176</t>
+          <t>std250</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MUHSINA</t>
+          <t>KABIDO</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BELLO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>MUSA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>RAHAMA</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>07038251084</t>
+          <t>08138424118</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1139,32 +1183,32 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>std177</t>
+          <t>std251</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>ADEROGBA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SAMIR</t>
+          <t>ADELESO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ZAIYANU</t>
+          <t>HASSANA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>07030927742</t>
+          <t>08038204448</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1181,27 +1225,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>std178</t>
+          <t>std252</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NA'IMA</t>
+          <t>ADEMOYE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AUWAL</t>
+          <t>ABIOLA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>FATHIA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>08033371313</t>
+          <t>08038184758</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1223,27 +1267,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>std179</t>
+          <t>std253</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NANA</t>
+          <t>YAHAYA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AUWAL</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ABDULHAKEEM</t>
+          <t>AISHA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>08036544182</t>
+          <t>07063498835</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1265,32 +1309,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>std180</t>
+          <t>std254</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RAJI</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>TUKUR</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>KAWU</t>
+          <t>MUFIDAT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>07061800414</t>
+          <t>07064220549</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1307,23 +1351,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>std181</t>
+          <t>std255</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RUTH</t>
+          <t>ISMAIL</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EZE</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>ISAH</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>FAIZA</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>08063155872</t>
+          <t>07063619332</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1345,23 +1393,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>std182</t>
+          <t>std256</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RUKKAIYA</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ABAMAMMAN</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>EFUA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AMIRA</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>08036134213</t>
+          <t>08033410008</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1383,23 +1435,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>std183</t>
+          <t>std257</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>YUSRA</t>
+          <t>OMADEFU</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ABDULRASHEED</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>ASIBI</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AMIRA</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>08023797649</t>
+          <t>08036057258</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1421,23 +1477,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>std184</t>
+          <t>std258</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ZAINAB</t>
+          <t>ADEYEMI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ALIYU</t>
+          <t>HEBBAHTULLAH</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>09186644664</t>
+          <t>08036261741</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1459,27 +1515,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>std185</t>
+          <t>std259</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ZAKIYYAH</t>
+          <t>DAMUSA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>UFEDOTOH</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>OMONYE</t>
+          <t>NANA K.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>08035290331</t>
+          <t>08065376751</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1501,23 +1557,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>std186</t>
+          <t>std260</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
+          <t>GALADIMA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>USMAN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>KHADIJA</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>09164925212</t>
+          <t>08144826092</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1539,32 +1599,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>std187</t>
+          <t>std261</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MUSA</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YUSUF</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>UMAR</t>
-        </is>
-      </c>
+          <t>UMMULKHAIR</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>07031940146</t>
+          <t>08030569524</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1581,23 +1637,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>std188</t>
+          <t>std262</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ADAMU</t>
+          <t>TAJUDEEN</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YAKUBU</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>ASIWAJU</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ABDULBASIT</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>09022340559</t>
+          <t>080095613348</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1619,28 +1679,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>std189</t>
+          <t>std263</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MOHAMMAD</t>
+          <t>MUHAMMED</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NASIR</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>OYIZA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>KHAIRET</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>07064493655</t>
+          <t>08072424291</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1657,27 +1721,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>std190</t>
+          <t>std264</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AHMAD</t>
+          <t>HABIBULLAH</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>AFFAN</t>
-        </is>
-      </c>
+          <t>ABDULMALIK</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>08068694226</t>
+          <t>08065544064</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1699,27 +1759,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>std191</t>
+          <t>std265</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ABDUL-QADIR</t>
+          <t>BABAKURA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>KHALIFA</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>KABIR</t>
-        </is>
-      </c>
+          <t>TIJJANI</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>08034800600</t>
+          <t>08067045013</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1729,7 +1785,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1741,23 +1797,23 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>std192</t>
+          <t>std266</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>MUSA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ABDULWAHAB</t>
+          <t>TAHIR</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>08077229624</t>
+          <t>08066441344</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1767,7 +1823,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1779,27 +1835,23 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>std193</t>
+          <t>std267</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>USMAN</t>
+          <t>KABIR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ADAMU</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>ISHAQ</t>
-        </is>
-      </c>
+          <t>SAIDUBABA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>08131449884</t>
+          <t>09119851571</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1809,7 +1861,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1821,27 +1873,27 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>std194</t>
+          <t>std268</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>IRFAN</t>
+          <t>SHEHU</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FARUK</t>
+          <t>RAMALAN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>IDIARO</t>
+          <t>SAABIR</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>08033707456</t>
+          <t>08035927011</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1851,7 +1903,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1863,23 +1915,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>std195</t>
+          <t>std269</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OMALE</t>
+          <t>AL-AMIN</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>JORDAN</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>O.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>AHMED</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>08073173763</t>
+          <t>08136552705</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1889,7 +1945,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1901,37 +1957,33 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>std196</t>
+          <t>std270</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UMMULKULTHUM</t>
+          <t>ZAHARADEEN</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HAYATU</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>WAZIRI</t>
-        </is>
-      </c>
+          <t>UMAR</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>08026329671</t>
+          <t>08035944688</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -1943,33 +1995,37 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>std197</t>
+          <t>std271</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MUHAMMED</t>
+          <t>AMINU</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HAUWA</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>MUSA</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>08033697673</t>
+          <t>08032889558</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -1981,33 +2037,37 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>std198</t>
+          <t>std272</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SUMIA</t>
+          <t>SADIQ</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MOMOD</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>ISMAIL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>07064174881</t>
+          <t>08033587358</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2019,27 +2079,23 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>std199</t>
+          <t>std273</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IDRIS</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MARYAM</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>RABIU</t>
-        </is>
-      </c>
+          <t>JAMILA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>08036077039</t>
+          <t>08036272740</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2049,7 +2105,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2061,27 +2117,27 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>std200</t>
+          <t>std274</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ABBAKURA</t>
+          <t>ABDURRAHMAN</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FATIMAH</t>
+          <t>NUMAT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ALI</t>
+          <t>MAIMUNAT</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>08032167508</t>
+          <t>08036040662</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2091,7 +2147,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2103,23 +2159,27 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>std201</t>
+          <t>std275</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ISMAIL</t>
+          <t>SAMBO</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LAMIA</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>HAJARA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AMINU</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>07063619332</t>
+          <t>08035887544</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2129,7 +2189,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2141,27 +2201,27 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>std202</t>
+          <t>std276</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IDOWU</t>
+          <t>SANI</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NIMATULLAHI</t>
+          <t>HAFSA</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>A.</t>
+          <t>BELLO</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>08036888250</t>
+          <t>07036576765</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2171,7 +2231,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2183,33 +2243,37 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>std203</t>
+          <t>std277</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SUNUSI</t>
+          <t>SALISU</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AMIR</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
+          <t>NANA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ASMAU</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>08166677184</t>
+          <t>07089903318</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2221,27 +2285,27 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>std204</t>
+          <t>std278</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ISMAIL</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UMMU</t>
+          <t>ZAINAB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SHURAIHA</t>
+          <t>AMINU</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>08032892838</t>
+          <t>08055262097</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2251,7 +2315,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2263,37 +2327,33 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>std205</t>
+          <t>std279</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UTHMAN</t>
+          <t>AMATULLAH</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>JAWAD</t>
-        </is>
-      </c>
+          <t>ABDULMALIK</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>08065474565</t>
+          <t>08036495912</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2305,27 +2365,27 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>std206</t>
+          <t>std280</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>MUKHTAR</t>
+          <t>IKAKA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AISHA</t>
+          <t>AHMED</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>AHMAD</t>
+          <t>BILKISU</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>08139191130</t>
+          <t>08033884440</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2335,7 +2395,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2347,27 +2407,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>std207</t>
+          <t>std281</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OLOPADE</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ABDUL</t>
+          <t>KABIR</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>WARIS</t>
+          <t>MUKHTAR</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>08165453077</t>
+          <t>08033912352</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2377,7 +2437,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2389,7 +2449,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>std208</t>
+          <t>std282</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2399,17 +2459,13 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>IDRIS</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>ABDULLAHI</t>
-        </is>
-      </c>
+          <t>HUSSAIN</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>08093871791</t>
+          <t>07035663576</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2419,7 +2475,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2431,37 +2487,33 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>std209</t>
+          <t>std283</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ABBAKURA</t>
+          <t>BASHIR</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FATIMA</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>ZAHRA</t>
-        </is>
-      </c>
+          <t>MAHMUD</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>08032109299</t>
+          <t>08032181310</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2473,33 +2525,37 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>std210</t>
+          <t>std284</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FATIMA</t>
+          <t>AMINU</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ABDULJABBAR</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>YASSAR</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>08027950448</t>
+          <t>08157275454</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_SILVER</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2511,37 +2567,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>std211</t>
+          <t>std285</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AISHA</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>GIREI</t>
-        </is>
-      </c>
+          <t>SA'AD</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>08036232351</t>
+          <t>08034000882</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2553,37 +2605,37 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>std212</t>
+          <t>std286</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>YUSRAH</t>
+          <t>ABAHI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
+          <t>WONDA</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>A.</t>
+          <t>U. ABDULSAMAD</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>08062602000</t>
+          <t>08066188131</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2595,37 +2647,37 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>std213</t>
+          <t>std287</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RAMLA</t>
+          <t>SHETTIMA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>YAHAYA</t>
+          <t>B.</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>YAKUBU</t>
+          <t>MUSTAPHA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>08064607626</t>
+          <t>08026994119</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2637,37 +2689,37 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>std214</t>
+          <t>std288</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SAFEEYAH</t>
+          <t>ADEYEMI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>MATTHEW</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>H.</t>
+          <t>ADESIRE</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>08028398915</t>
+          <t>08032190197</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2679,23 +2731,23 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>std215</t>
+          <t>std289</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>UMMULKHAIR</t>
+          <t>KHAIRAT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ZUBAIRU</t>
+          <t>BADAMASI</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>08035952585</t>
+          <t>08032245423</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2705,7 +2757,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2717,37 +2769,33 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>std216</t>
+          <t>std290</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FAIZA</t>
+          <t>MUHAMMAD</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MUDARRIFU</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>F.</t>
-        </is>
-      </c>
+          <t>SULEIMAN</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>08015404681</t>
+          <t>07029636558</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2759,27 +2807,27 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>std217</t>
+          <t>std291</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AISHA</t>
+          <t>ABDULLAHI</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>POPOOLA</t>
+          <t>UMAIMAH</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>IREBAMI</t>
+          <t>ZHEOMA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>07022766863</t>
+          <t>08035885141</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2789,7 +2837,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2801,37 +2849,37 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>std218</t>
+          <t>std292</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HAFSAT</t>
+          <t>SAED</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>A.</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>HASSAN</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>08003805010</t>
+          <t>08035973912</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2843,37 +2891,33 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>std219</t>
+          <t>std293</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RAYYANNA</t>
+          <t>AKINLOYE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ALLI</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>ADEJOUN</t>
-        </is>
-      </c>
+          <t>GODSWILL</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>07067020234</t>
+          <t>08069353822</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Male</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2885,27 +2929,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>std220</t>
+          <t>std294</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SAFEEYAH</t>
+          <t>RUKAYYA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SAEED</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>YAHAYA</t>
-        </is>
-      </c>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>08033110134</t>
+          <t>08027163415</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2915,7 +2955,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2927,33 +2967,37 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>std221</t>
+          <t>std295</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ABDULGANIYU</t>
+          <t>FARZEENAH</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AUDU</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>T.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>08023323811</t>
+          <t>08033577423</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2965,33 +3009,33 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>std222</t>
+          <t>std296</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ZAYYAN</t>
+          <t>OLAGUNJU</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ZAYYAN</t>
+          <t>FIRDAUS</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>07068800574</t>
+          <t>08138369857</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3003,37 +3047,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>std223</t>
+          <t>std297</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
+          <t>OLUFEMOH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AUWAL</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>BELLO</t>
-        </is>
-      </c>
+          <t>MUNIRAT</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>08034948449</t>
+          <t>08026160230</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3045,37 +3085,37 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>std224</t>
+          <t>std298</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MURTALA</t>
+          <t>KHADIJAH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>HALIRU</t>
+          <t>BABAYARO</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>AMBURSA</t>
+          <t>MUKHTAR</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>08068067508</t>
+          <t>07063104355</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3087,33 +3127,37 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>std225</t>
+          <t>std299</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>YAHAYA</t>
+          <t>SABIRAH</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HABUFARI</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>HASSAN</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ABDULLAH</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>08099944553</t>
+          <t>08034204648</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3125,23 +3169,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>std226</t>
+          <t>std300</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BAWA</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MAHMUD</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>AMINU</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>SANJUMA</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>07068816607</t>
+          <t>08034132060</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3151,7 +3199,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3163,27 +3211,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>std227</t>
+          <t>std301</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FARHAN</t>
+          <t>IBRAHIM</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+          <t>TAHIR</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>08036422227</t>
+          <t>07035485005</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3193,7 +3237,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3205,27 +3249,27 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>std228</t>
+          <t>std302</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ABBAS</t>
+          <t>KOREDE</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ABBAS</t>
+          <t>SALAU</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>BELLO</t>
+          <t>ABDULLAHI</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>07034448544</t>
+          <t>08166294250</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3235,7 +3279,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3247,23 +3291,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>std229</t>
+          <t>std303</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SANI</t>
+          <t>ZANSHIRU</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MUHAMMAD</t>
+          <t>YUSUF</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>08030733215</t>
+          <t>08072602070</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3273,7 +3317,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3285,37 +3329,37 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>std230</t>
+          <t>std304</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SALISU</t>
+          <t>JUNAIRIYYA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>YUSUF</t>
+          <t>RABIU</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BAYERO</t>
+          <t>IDRIS</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>08199944444</t>
+          <t>07039229772</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3327,33 +3371,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>std231</t>
+          <t>std305</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SALIHU</t>
+          <t>ABUBAKAR</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ABUBAKAR</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>FATIMA</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>JASMINE</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>08035839220</t>
+          <t>08033365925</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Female</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3365,23 +3413,27 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>std232</t>
+          <t>std306</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ABDULHAMID</t>
+          <t>ABDULMALIK</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>IBRAHIM</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>SAMIR</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AHMAD</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>08072229644</t>
+          <t>08057265792</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3391,7 +3443,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SS1_DIAMOND</t>
+          <t>SS1_GOLD</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3403,43 +3455,1621 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>std233</t>
+          <t>std307</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
+          <t>AUWAL</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>AISHA</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>IBRAHIM</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>08036173202</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SS1_GOLD</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>std308</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>BENITA</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>PETER</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>08069102556</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SS1_GOLD</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>std309</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ISHAQ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>A.</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>QASIM USMAN</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>08033191149</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>SS1_GOLD</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>std310</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MUHAMMED</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SHEHU</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>080062447500</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>SS1_GOLD</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>std311</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LUQMAN</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>ALAMIN</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>07032620527</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>SS1_GOLD</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>std312</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>ABUBAKAR</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>HABIBA</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>08041326079</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>SS1_GOLD</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>std313</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>MUSTAPHA</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>FATIMA</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>08067757775</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SS1_GOLD</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>std314</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SANI</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>FAZEELAT</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>08030799725</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>std315</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SHOFOLUWE</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>O.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NEEMATULLAH</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>07066229010</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>std316</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ABBA</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MAMMAN</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>FATIMA</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>08039725582</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>std317</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>FUAD</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ADEYEMI</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>FAUZI</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>080130680040</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>std318</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>BASHIR</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
           <t>ABDULLAHI</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>DANMALAM</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>09090424235</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>SS1_DIAMOND</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>080372667696</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>std319</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>MARAFIA</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ATTAHIR</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>0817808006</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>std320</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>ADEBAYO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>DAMILOLA</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>FATHIA</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>090388330432</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>std321</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SHAMSU</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>ZIYAHULLHAQ</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>08037031114</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>std322</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>JOHN</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>DAVID</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>08034414206</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>std323</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>KOREDE</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SAMUEL</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>07053262036</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>std324</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>AJAO</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>UMAR</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>07034372559</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>std325</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>ABDULLAHI</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ALIYU</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>080369891390</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>std326</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>FARUK</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>NDAYAKO</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SHAFI</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>08032013860</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>std327</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SANI</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>WAKILI</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>UMAR</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>080331541112</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>std328</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ADEYEMI</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ADENIKE</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NAJA'A</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>08067371845</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>std329</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>AJAO</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>FAUZIYA</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>08034372559</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>std330</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ABDULLAHI</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SADIQ</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>08036989390</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>std331</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>HASHIM</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>MUHAMMED</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>YUNUS</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>08094198290</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>std332</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>UMAR</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>MUHAMMAD</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>08037876862</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>std333</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ISA</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>HAUWA</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>080359150327</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>std334</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SANUSI</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SUMAYYA</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>08059706494</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>std335</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>BELLO</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MARYAM</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>MADINAH</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>08188720987</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>std336</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>AMINU</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>YASSAR</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>USMAN</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>091338237</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>std337</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>MUSBAHU</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>YAKUBU</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AHMAD</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>080552442908</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>std338</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>ZAYYAN</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>MUHSIN</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>07068866548</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>std339</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>ADESHINA</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>CASSANDRA</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>HABIBA</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0817251384</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>std340</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>BASHIR</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>MAHMUD</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>HAUWA</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>08036587954</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>std341</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ALIYU</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>AHMAD</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>08085566519</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>std342</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ALIYU</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>LOLO</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>FATIHA</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>08035899950</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>std343</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ALIYU</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SHAFI</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>UMAR</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>0707306375</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>std344</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ALHASSAN</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>AALIYAH</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>UMMT</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>080550885141</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>std345</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ABUBAKAR</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>AMAL</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>AISHA</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>0803159021</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>SS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>std346</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SANUSI</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ABDULRAHMAN</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>08020850490</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>SS1_B/C</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
         <is>
           <t>SS1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H75"/>
+  <autoFilter ref="A1:H114"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>